--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="19200" windowHeight="8055"/>
   </bookViews>
   <sheets>
-    <sheet name="candidate_points" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Longitude</t>
   </si>
   <si>
     <t>Latitude</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
 </sst>
 </file>
@@ -500,9 +503,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,8 +649,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -704,221 +706,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -928,7 +716,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -938,39 +726,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1002,7 +790,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1037,7 +824,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1049,131 +835,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1185,255 +1000,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>121.1884325</v>
+        <v>121.194746</v>
       </c>
       <c r="B2">
-        <v>31.27468382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>31.2809145</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>121.1968505</v>
       </c>
       <c r="B3">
-        <v>31.27468382</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>31.2809145</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
-        <v>121.2052685</v>
+        <v>121.198955</v>
       </c>
       <c r="B4">
-        <v>31.27468382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>31.2809145</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
-        <v>121.2094775</v>
+        <v>121.2042162</v>
       </c>
       <c r="B5">
-        <v>31.27468382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>31.29804887</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>121.1957982</v>
       </c>
       <c r="B6">
         <v>31.27624149</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
-        <v>121.2021117</v>
+        <v>121.2094775</v>
       </c>
       <c r="B7">
-        <v>31.29804887</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>31.27468382</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
-        <v>121.2042162</v>
+        <v>121.2052685</v>
       </c>
       <c r="B8">
-        <v>31.29804887</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>31.27468382</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
-        <v>121.198955</v>
+        <v>121.1968505</v>
       </c>
       <c r="B9">
-        <v>31.2809145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>31.27468382</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
-        <v>121.1968505</v>
+        <v>121.2210522</v>
       </c>
       <c r="B10">
-        <v>31.2809145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>31.27312615</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
-        <v>121.194746</v>
+        <v>121.2252612</v>
       </c>
       <c r="B11">
-        <v>31.2809145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>31.27624149</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>121.2221045</v>
+        <v>121.2263135</v>
       </c>
       <c r="B12">
         <v>31.27468382</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>121.224209</v>
       </c>
       <c r="B13">
         <v>31.27468382</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
+        <v>121.241045</v>
+      </c>
+      <c r="B14">
+        <v>31.26845314</v>
+      </c>
+      <c r="C14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>121.2431495</v>
+      </c>
+      <c r="B15">
+        <v>31.26845314</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>121.2442017</v>
+      </c>
+      <c r="B16">
+        <v>31.27001081</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>121.2263135</v>
       </c>
-      <c r="B14">
-        <v>31.27468382</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>121.2252612</v>
-      </c>
-      <c r="B15">
-        <v>31.27624149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
+      <c r="B17">
+        <v>31.27156848</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>121.2231567</v>
+      </c>
+      <c r="B18">
+        <v>31.28870285</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>121.2210522</v>
       </c>
-      <c r="B16">
-        <v>31.27312615</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
+      <c r="B19">
+        <v>31.28870285</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>121.2221045</v>
+      </c>
+      <c r="B20">
+        <v>31.28714518</v>
+      </c>
+      <c r="C20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>121.232627</v>
       </c>
-      <c r="B17">
-        <v>31.26845314</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>121.2263135</v>
-      </c>
-      <c r="B18">
-        <v>31.27156848</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>121.2442017</v>
-      </c>
-      <c r="B19">
-        <v>31.27001081</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>121.2431495</v>
-      </c>
-      <c r="B20">
-        <v>31.26845314</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>121.241045</v>
-      </c>
       <c r="B21">
-        <v>31.26845314</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>31.28402984</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>121.2294702</v>
+        <v>121.253672</v>
       </c>
       <c r="B22">
-        <v>31.28247217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>31.2653378</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
-        <v>121.232627</v>
+        <v>121.2515675</v>
       </c>
       <c r="B23">
-        <v>31.28402984</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>31.2653378</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
-        <v>121.2221045</v>
+        <v>121.249463</v>
       </c>
       <c r="B24">
-        <v>31.28714518</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>31.2653378</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
-        <v>121.2210522</v>
+        <v>121.2473585</v>
       </c>
       <c r="B25">
-        <v>31.28870285</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>121.2231567</v>
-      </c>
-      <c r="B26">
-        <v>31.28870285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>121.245254</v>
-      </c>
-      <c r="B27">
         <v>31.2653378</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>121.2473585</v>
-      </c>
-      <c r="B28">
-        <v>31.2653378</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>121.249463</v>
-      </c>
-      <c r="B29">
-        <v>31.2653378</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>121.2515675</v>
-      </c>
-      <c r="B30">
-        <v>31.2653378</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>121.253672</v>
-      </c>
-      <c r="B31">
-        <v>31.2653378</v>
+      <c r="C25">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -27,7 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
   <si>
     <t>Longitude</t>
   </si>
@@ -48,7 +54,21 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,12 +415,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -519,141 +554,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1000,281 +1039,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
         <v>121.194746</v>
       </c>
-      <c r="B2">
+      <c r="D2" s="3">
         <v>31.2809145</v>
       </c>
-      <c r="C2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
         <v>121.1968505</v>
       </c>
-      <c r="B3">
+      <c r="D3" s="3">
         <v>31.2809145</v>
       </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
         <v>121.198955</v>
       </c>
-      <c r="B4">
+      <c r="D4" s="3">
         <v>31.2809145</v>
       </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3">
         <v>121.2042162</v>
       </c>
-      <c r="B5">
+      <c r="D5" s="3">
         <v>31.29804887</v>
       </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
         <v>121.1957982</v>
       </c>
-      <c r="B6">
+      <c r="D6" s="3">
         <v>31.27624149</v>
       </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3">
         <v>121.2094775</v>
       </c>
-      <c r="B7">
+      <c r="D7" s="3">
         <v>31.27468382</v>
       </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3">
         <v>121.2052685</v>
       </c>
-      <c r="B8">
+      <c r="D8" s="3">
         <v>31.27468382</v>
       </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3">
         <v>121.1968505</v>
       </c>
-      <c r="B9">
+      <c r="D9" s="3">
         <v>31.27468382</v>
       </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
+      <c r="E9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
         <v>121.2210522</v>
       </c>
-      <c r="B10">
+      <c r="D10" s="3">
         <v>31.27312615</v>
       </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
+      <c r="E10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
         <v>121.2252612</v>
       </c>
-      <c r="B11">
+      <c r="D11" s="3">
         <v>31.27624149</v>
       </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3">
         <v>121.2263135</v>
       </c>
-      <c r="B12">
+      <c r="D12" s="3">
         <v>31.27468382</v>
       </c>
-      <c r="C12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
+      <c r="E12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3">
         <v>121.224209</v>
       </c>
-      <c r="B13">
+      <c r="D13" s="3">
         <v>31.27468382</v>
       </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
+      <c r="E13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
         <v>121.241045</v>
       </c>
-      <c r="B14">
+      <c r="D14" s="3">
         <v>31.26845314</v>
       </c>
-      <c r="C14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
         <v>121.2431495</v>
       </c>
-      <c r="B15">
+      <c r="D15" s="3">
         <v>31.26845314</v>
       </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
         <v>121.2442017</v>
       </c>
-      <c r="B16">
+      <c r="D16" s="3">
         <v>31.27001081</v>
       </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
+      <c r="E16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3">
         <v>121.2263135</v>
       </c>
-      <c r="B17">
+      <c r="D17" s="3">
         <v>31.27156848</v>
       </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
+      <c r="E17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
         <v>121.2231567</v>
       </c>
-      <c r="B18">
+      <c r="D18" s="3">
         <v>31.28870285</v>
       </c>
-      <c r="C18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
+      <c r="E18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3">
         <v>121.2210522</v>
       </c>
-      <c r="B19">
+      <c r="D19" s="3">
         <v>31.28870285</v>
       </c>
-      <c r="C19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
+      <c r="E19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
         <v>121.2221045</v>
       </c>
-      <c r="B20">
+      <c r="D20" s="3">
         <v>31.28714518</v>
       </c>
-      <c r="C20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
+      <c r="E20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3">
         <v>121.232627</v>
       </c>
-      <c r="B21">
+      <c r="D21" s="3">
         <v>31.28402984</v>
       </c>
-      <c r="C21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
+      <c r="E21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
         <v>121.253672</v>
       </c>
-      <c r="B22">
+      <c r="D22" s="3">
         <v>31.2653378</v>
       </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>5</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
         <v>121.2515675</v>
       </c>
-      <c r="B23">
+      <c r="D23" s="3">
         <v>31.2653378</v>
       </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>5</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
         <v>121.249463</v>
       </c>
-      <c r="B24">
+      <c r="D24" s="3">
         <v>31.2653378</v>
       </c>
-      <c r="C24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
+      <c r="E24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>5</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
         <v>121.2473585</v>
       </c>
-      <c r="B25">
+      <c r="D25" s="3">
         <v>31.2653378</v>
       </c>
-      <c r="C25">
+      <c r="E25">
         <v>0.5</v>
       </c>
     </row>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -1041,6 +1041,10 @@
   <sheetPr/>
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="16.2654867256637" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -54,7 +54,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,13 +65,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -554,133 +547,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -692,7 +685,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1077,7 +1070,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1094,7 +1087,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1111,7 +1104,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1128,7 +1121,7 @@
         <v>31.29804887</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1145,7 +1138,7 @@
         <v>31.27624149</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1162,7 +1155,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1179,7 +1172,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1196,7 +1189,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1213,7 +1206,7 @@
         <v>31.27312615</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1230,7 +1223,7 @@
         <v>31.27624149</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1247,7 +1240,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1264,7 +1257,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1281,7 +1274,7 @@
         <v>31.26845314</v>
       </c>
       <c r="E14">
-        <v>0.5</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1298,7 +1291,7 @@
         <v>31.26845314</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1315,7 +1308,7 @@
         <v>31.27001081</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1332,7 +1325,7 @@
         <v>31.27156848</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1349,7 +1342,7 @@
         <v>31.28870285</v>
       </c>
       <c r="E18">
-        <v>0.5</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1366,7 +1359,7 @@
         <v>31.28870285</v>
       </c>
       <c r="E19">
-        <v>0.5</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1383,7 +1376,7 @@
         <v>31.28714518</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1400,7 +1393,7 @@
         <v>31.28402984</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1417,7 +1410,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1434,7 +1427,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E23">
-        <v>0.5</v>
+        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1451,7 +1444,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E24">
-        <v>0.5</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1468,7 +1461,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E25">
-        <v>0.5</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055"/>
+    <workbookView windowWidth="21094" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1033,9 +1033,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="16.2654867256637" customWidth="1"/>
+    <col min="3" max="3" width="16.2612612612613" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1070,7 +1070,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1087,7 +1087,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E3">
-        <v>501</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1104,7 +1104,7 @@
         <v>31.2809145</v>
       </c>
       <c r="E4">
-        <v>502</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1121,7 +1121,7 @@
         <v>31.29804887</v>
       </c>
       <c r="E5">
-        <v>503</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1138,7 +1138,7 @@
         <v>31.27624149</v>
       </c>
       <c r="E6">
-        <v>504</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1155,7 +1155,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E7">
-        <v>505</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1172,7 +1172,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E8">
-        <v>506</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1189,7 +1189,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E9">
-        <v>507</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1206,7 +1206,7 @@
         <v>31.27312615</v>
       </c>
       <c r="E10">
-        <v>508</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1223,7 +1223,7 @@
         <v>31.27624149</v>
       </c>
       <c r="E11">
-        <v>509</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1240,7 +1240,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E12">
-        <v>510</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1257,7 +1257,7 @@
         <v>31.27468382</v>
       </c>
       <c r="E13">
-        <v>511</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1274,7 +1274,7 @@
         <v>31.26845314</v>
       </c>
       <c r="E14">
-        <v>512</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1291,7 +1291,7 @@
         <v>31.26845314</v>
       </c>
       <c r="E15">
-        <v>513</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1308,7 +1308,7 @@
         <v>31.27001081</v>
       </c>
       <c r="E16">
-        <v>514</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1325,7 +1325,7 @@
         <v>31.27156848</v>
       </c>
       <c r="E17">
-        <v>515</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1342,7 +1342,7 @@
         <v>31.28870285</v>
       </c>
       <c r="E18">
-        <v>516</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1359,7 +1359,7 @@
         <v>31.28870285</v>
       </c>
       <c r="E19">
-        <v>517</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1376,7 +1376,7 @@
         <v>31.28714518</v>
       </c>
       <c r="E20">
-        <v>518</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1393,7 +1393,7 @@
         <v>31.28402984</v>
       </c>
       <c r="E21">
-        <v>519</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1410,7 +1410,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E22">
-        <v>520</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1427,7 +1427,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E23">
-        <v>521</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1444,7 +1444,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E24">
-        <v>522</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1461,7 +1461,7 @@
         <v>31.2653378</v>
       </c>
       <c r="E25">
-        <v>523</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>class</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>模拟平均需求</t>
   </si>
 </sst>
 </file>
@@ -1032,14 +1035,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="4"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.2612612612613" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10.5495495495495"/>
+    <col min="7" max="7" width="10.5495495495495"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,8 +1060,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -1070,10 +1078,17 @@
         <v>31.2809145</v>
       </c>
       <c r="E2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>158.19904</v>
+      </c>
+      <c r="F2">
+        <v>3.1152</v>
+      </c>
+      <c r="G2">
+        <f>100*(1.42+0.052*F2)</f>
+        <v>158.19904</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -1087,10 +1102,17 @@
         <v>31.2809145</v>
       </c>
       <c r="E3">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>161.06528</v>
+      </c>
+      <c r="F3">
+        <v>3.6664</v>
+      </c>
+      <c r="G3">
+        <f>100*(1.42+0.052*F3)</f>
+        <v>161.06528</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1104,10 +1126,17 @@
         <v>31.2809145</v>
       </c>
       <c r="E4">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>155.8372</v>
+      </c>
+      <c r="F4">
+        <v>2.661</v>
+      </c>
+      <c r="G4">
+        <f>100*(1.42+0.052*F4)</f>
+        <v>155.8372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
         <v>0</v>
       </c>
@@ -1121,10 +1150,17 @@
         <v>31.29804887</v>
       </c>
       <c r="E5">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>330.13496</v>
+      </c>
+      <c r="F5">
+        <v>36.1798</v>
+      </c>
+      <c r="G5">
+        <f>100*(1.42+0.052*F5)</f>
+        <v>330.13496</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1138,10 +1174,17 @@
         <v>31.27624149</v>
       </c>
       <c r="E6">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>169.495</v>
+      </c>
+      <c r="F6">
+        <v>5.2875</v>
+      </c>
+      <c r="G6">
+        <f>100*(1.42+0.052*F6)</f>
+        <v>169.495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -1155,10 +1198,17 @@
         <v>31.27468382</v>
       </c>
       <c r="E7">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>187.7938</v>
+      </c>
+      <c r="F7">
+        <v>8.8065</v>
+      </c>
+      <c r="G7">
+        <f>100*(1.42+0.052*F7)</f>
+        <v>187.7938</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1172,10 +1222,17 @@
         <v>31.27468382</v>
       </c>
       <c r="E8">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>162.78284</v>
+      </c>
+      <c r="F8">
+        <v>3.9967</v>
+      </c>
+      <c r="G8">
+        <f>100*(1.42+0.052*F8)</f>
+        <v>162.78284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1189,10 +1246,17 @@
         <v>31.27468382</v>
       </c>
       <c r="E9">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>174.2244</v>
+      </c>
+      <c r="F9">
+        <v>6.197</v>
+      </c>
+      <c r="G9">
+        <f>100*(1.42+0.052*F9)</f>
+        <v>174.2244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1206,10 +1270,17 @@
         <v>31.27312615</v>
       </c>
       <c r="E10">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>174.01796</v>
+      </c>
+      <c r="F10">
+        <v>6.1573</v>
+      </c>
+      <c r="G10">
+        <f>100*(1.42+0.052*F10)</f>
+        <v>174.01796</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -1223,10 +1294,17 @@
         <v>31.27624149</v>
       </c>
       <c r="E11">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>184.1746</v>
+      </c>
+      <c r="F11">
+        <v>8.1105</v>
+      </c>
+      <c r="G11">
+        <f>100*(1.42+0.052*F11)</f>
+        <v>184.1746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1240,10 +1318,17 @@
         <v>31.27468382</v>
       </c>
       <c r="E12">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>167.6932</v>
+      </c>
+      <c r="F12">
+        <v>4.941</v>
+      </c>
+      <c r="G12">
+        <f>100*(1.42+0.052*F12)</f>
+        <v>167.6932</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1257,10 +1342,17 @@
         <v>31.27468382</v>
       </c>
       <c r="E13">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>165.87944</v>
+      </c>
+      <c r="F13">
+        <v>4.5922</v>
+      </c>
+      <c r="G13">
+        <f>100*(1.42+0.052*F13)</f>
+        <v>165.87944</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="3">
         <v>3</v>
       </c>
@@ -1274,10 +1366,17 @@
         <v>31.26845314</v>
       </c>
       <c r="E14">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>159.03156</v>
+      </c>
+      <c r="F14">
+        <v>3.2753</v>
+      </c>
+      <c r="G14">
+        <f>100*(1.42+0.052*F14)</f>
+        <v>159.03156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="3">
         <v>3</v>
       </c>
@@ -1291,10 +1390,17 @@
         <v>31.26845314</v>
       </c>
       <c r="E15">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>149.7038</v>
+      </c>
+      <c r="F15">
+        <v>1.4815</v>
+      </c>
+      <c r="G15">
+        <f>100*(1.42+0.052*F15)</f>
+        <v>149.7038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1308,10 +1414,17 @@
         <v>31.27001081</v>
       </c>
       <c r="E16">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>159.35448</v>
+      </c>
+      <c r="F16">
+        <v>3.3374</v>
+      </c>
+      <c r="G16">
+        <f>100*(1.42+0.052*F16)</f>
+        <v>159.35448</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="3">
         <v>3</v>
       </c>
@@ -1325,10 +1438,17 @@
         <v>31.27156848</v>
       </c>
       <c r="E17">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>173.43868</v>
+      </c>
+      <c r="F17">
+        <v>6.0459</v>
+      </c>
+      <c r="G17">
+        <f>100*(1.42+0.052*F17)</f>
+        <v>173.43868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="3">
         <v>4</v>
       </c>
@@ -1342,10 +1462,17 @@
         <v>31.28870285</v>
       </c>
       <c r="E18">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>151.3444</v>
+      </c>
+      <c r="F18">
+        <v>1.797</v>
+      </c>
+      <c r="G18">
+        <f>100*(1.42+0.052*F18)</f>
+        <v>151.3444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="3">
         <v>4</v>
       </c>
@@ -1359,10 +1486,17 @@
         <v>31.28870285</v>
       </c>
       <c r="E19">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>298.03016</v>
+      </c>
+      <c r="F19">
+        <v>30.0058</v>
+      </c>
+      <c r="G19">
+        <f>100*(1.42+0.052*F19)</f>
+        <v>298.03016</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="3">
         <v>4</v>
       </c>
@@ -1376,10 +1510,17 @@
         <v>31.28714518</v>
       </c>
       <c r="E20">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>452.61784</v>
+      </c>
+      <c r="F20">
+        <v>59.7342</v>
+      </c>
+      <c r="G20">
+        <f>100*(1.42+0.052*F20)</f>
+        <v>452.61784</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="3">
         <v>4</v>
       </c>
@@ -1393,10 +1534,17 @@
         <v>31.28402984</v>
       </c>
       <c r="E21">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>271.116</v>
+      </c>
+      <c r="F21">
+        <v>24.83</v>
+      </c>
+      <c r="G21">
+        <f>100*(1.42+0.052*F21)</f>
+        <v>271.116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="3">
         <v>5</v>
       </c>
@@ -1410,10 +1558,17 @@
         <v>31.2653378</v>
       </c>
       <c r="E22">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>180.50756</v>
+      </c>
+      <c r="F22">
+        <v>7.4053</v>
+      </c>
+      <c r="G22">
+        <f>100*(1.42+0.052*F22)</f>
+        <v>180.50756</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="3">
         <v>5</v>
       </c>
@@ -1427,10 +1582,17 @@
         <v>31.2653378</v>
       </c>
       <c r="E23">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>160.0908</v>
+      </c>
+      <c r="F23">
+        <v>3.479</v>
+      </c>
+      <c r="G23">
+        <f>100*(1.42+0.052*F23)</f>
+        <v>160.0908</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="3">
         <v>5</v>
       </c>
@@ -1444,10 +1606,17 @@
         <v>31.2653378</v>
       </c>
       <c r="E24">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>180.48</v>
+      </c>
+      <c r="F24">
+        <v>7.4</v>
+      </c>
+      <c r="G24">
+        <f>100*(1.42+0.052*F24)</f>
+        <v>180.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="3">
         <v>5</v>
       </c>
@@ -1461,10 +1630,21 @@
         <v>31.2653378</v>
       </c>
       <c r="E25">
-        <v>223</v>
+        <v>159.6046</v>
+      </c>
+      <c r="F25">
+        <v>3.3855</v>
+      </c>
+      <c r="G25">
+        <f>100*(1.42+0.052*F25)</f>
+        <v>159.6046</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:G25">
+    <sortCondition ref="A2:A25"/>
+    <sortCondition ref="B2:B25"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -1078,14 +1078,14 @@
         <v>31.2809145</v>
       </c>
       <c r="E2">
-        <v>158.19904</v>
+        <v>155.08384</v>
       </c>
       <c r="F2">
         <v>3.1152</v>
       </c>
       <c r="G2">
-        <f>100*(1.42+0.052*F2)</f>
-        <v>158.19904</v>
+        <f>100*(1.42+0.042*F2)</f>
+        <v>155.08384</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1102,14 +1102,14 @@
         <v>31.2809145</v>
       </c>
       <c r="E3">
-        <v>161.06528</v>
+        <v>157.39888</v>
       </c>
       <c r="F3">
         <v>3.6664</v>
       </c>
       <c r="G3">
-        <f>100*(1.42+0.052*F3)</f>
-        <v>161.06528</v>
+        <f t="shared" ref="G3:G25" si="0">100*(1.42+0.042*F3)</f>
+        <v>157.39888</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1126,14 +1126,14 @@
         <v>31.2809145</v>
       </c>
       <c r="E4">
-        <v>155.8372</v>
+        <v>153.1762</v>
       </c>
       <c r="F4">
         <v>2.661</v>
       </c>
       <c r="G4">
-        <f>100*(1.42+0.052*F4)</f>
-        <v>155.8372</v>
+        <f t="shared" si="0"/>
+        <v>153.1762</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1150,14 +1150,14 @@
         <v>31.29804887</v>
       </c>
       <c r="E5">
-        <v>330.13496</v>
+        <v>293.95516</v>
       </c>
       <c r="F5">
         <v>36.1798</v>
       </c>
       <c r="G5">
-        <f>100*(1.42+0.052*F5)</f>
-        <v>330.13496</v>
+        <f t="shared" si="0"/>
+        <v>293.95516</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1174,14 +1174,14 @@
         <v>31.27624149</v>
       </c>
       <c r="E6">
-        <v>169.495</v>
+        <v>164.2075</v>
       </c>
       <c r="F6">
         <v>5.2875</v>
       </c>
       <c r="G6">
-        <f>100*(1.42+0.052*F6)</f>
-        <v>169.495</v>
+        <f t="shared" si="0"/>
+        <v>164.2075</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1198,14 +1198,14 @@
         <v>31.27468382</v>
       </c>
       <c r="E7">
-        <v>187.7938</v>
+        <v>178.9873</v>
       </c>
       <c r="F7">
         <v>8.8065</v>
       </c>
       <c r="G7">
-        <f>100*(1.42+0.052*F7)</f>
-        <v>187.7938</v>
+        <f t="shared" si="0"/>
+        <v>178.9873</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1222,14 +1222,14 @@
         <v>31.27468382</v>
       </c>
       <c r="E8">
-        <v>162.78284</v>
+        <v>158.78614</v>
       </c>
       <c r="F8">
         <v>3.9967</v>
       </c>
       <c r="G8">
-        <f>100*(1.42+0.052*F8)</f>
-        <v>162.78284</v>
+        <f t="shared" si="0"/>
+        <v>158.78614</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1246,14 +1246,14 @@
         <v>31.27468382</v>
       </c>
       <c r="E9">
-        <v>174.2244</v>
+        <v>168.0274</v>
       </c>
       <c r="F9">
         <v>6.197</v>
       </c>
       <c r="G9">
-        <f>100*(1.42+0.052*F9)</f>
-        <v>174.2244</v>
+        <f t="shared" si="0"/>
+        <v>168.0274</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1270,14 +1270,14 @@
         <v>31.27312615</v>
       </c>
       <c r="E10">
-        <v>174.01796</v>
+        <v>167.86066</v>
       </c>
       <c r="F10">
         <v>6.1573</v>
       </c>
       <c r="G10">
-        <f>100*(1.42+0.052*F10)</f>
-        <v>174.01796</v>
+        <f t="shared" si="0"/>
+        <v>167.86066</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1294,14 +1294,14 @@
         <v>31.27624149</v>
       </c>
       <c r="E11">
-        <v>184.1746</v>
+        <v>176.0641</v>
       </c>
       <c r="F11">
         <v>8.1105</v>
       </c>
       <c r="G11">
-        <f>100*(1.42+0.052*F11)</f>
-        <v>184.1746</v>
+        <f t="shared" si="0"/>
+        <v>176.0641</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1318,14 +1318,14 @@
         <v>31.27468382</v>
       </c>
       <c r="E12">
-        <v>167.6932</v>
+        <v>162.7522</v>
       </c>
       <c r="F12">
         <v>4.941</v>
       </c>
       <c r="G12">
-        <f>100*(1.42+0.052*F12)</f>
-        <v>167.6932</v>
+        <f t="shared" si="0"/>
+        <v>162.7522</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1342,14 +1342,14 @@
         <v>31.27468382</v>
       </c>
       <c r="E13">
-        <v>165.87944</v>
+        <v>161.28724</v>
       </c>
       <c r="F13">
         <v>4.5922</v>
       </c>
       <c r="G13">
-        <f>100*(1.42+0.052*F13)</f>
-        <v>165.87944</v>
+        <f t="shared" si="0"/>
+        <v>161.28724</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1366,14 +1366,14 @@
         <v>31.26845314</v>
       </c>
       <c r="E14">
-        <v>159.03156</v>
+        <v>155.75626</v>
       </c>
       <c r="F14">
         <v>3.2753</v>
       </c>
       <c r="G14">
-        <f>100*(1.42+0.052*F14)</f>
-        <v>159.03156</v>
+        <f t="shared" si="0"/>
+        <v>155.75626</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1390,14 +1390,14 @@
         <v>31.26845314</v>
       </c>
       <c r="E15">
-        <v>149.7038</v>
+        <v>148.2223</v>
       </c>
       <c r="F15">
         <v>1.4815</v>
       </c>
       <c r="G15">
-        <f>100*(1.42+0.052*F15)</f>
-        <v>149.7038</v>
+        <f t="shared" si="0"/>
+        <v>148.2223</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1414,14 +1414,14 @@
         <v>31.27001081</v>
       </c>
       <c r="E16">
-        <v>159.35448</v>
+        <v>156.01708</v>
       </c>
       <c r="F16">
         <v>3.3374</v>
       </c>
       <c r="G16">
-        <f>100*(1.42+0.052*F16)</f>
-        <v>159.35448</v>
+        <f t="shared" si="0"/>
+        <v>156.01708</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1438,14 +1438,14 @@
         <v>31.27156848</v>
       </c>
       <c r="E17">
-        <v>173.43868</v>
+        <v>167.39278</v>
       </c>
       <c r="F17">
         <v>6.0459</v>
       </c>
       <c r="G17">
-        <f>100*(1.42+0.052*F17)</f>
-        <v>173.43868</v>
+        <f t="shared" si="0"/>
+        <v>167.39278</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1462,14 +1462,14 @@
         <v>31.28870285</v>
       </c>
       <c r="E18">
-        <v>151.3444</v>
+        <v>149.5474</v>
       </c>
       <c r="F18">
         <v>1.797</v>
       </c>
       <c r="G18">
-        <f>100*(1.42+0.052*F18)</f>
-        <v>151.3444</v>
+        <f t="shared" si="0"/>
+        <v>149.5474</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1486,14 +1486,14 @@
         <v>31.28870285</v>
       </c>
       <c r="E19">
-        <v>298.03016</v>
+        <v>268.02436</v>
       </c>
       <c r="F19">
         <v>30.0058</v>
       </c>
       <c r="G19">
-        <f>100*(1.42+0.052*F19)</f>
-        <v>298.03016</v>
+        <f t="shared" si="0"/>
+        <v>268.02436</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1510,14 +1510,14 @@
         <v>31.28714518</v>
       </c>
       <c r="E20">
-        <v>452.61784</v>
+        <v>392.88364</v>
       </c>
       <c r="F20">
         <v>59.7342</v>
       </c>
       <c r="G20">
-        <f>100*(1.42+0.052*F20)</f>
-        <v>452.61784</v>
+        <f t="shared" si="0"/>
+        <v>392.88364</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1534,14 +1534,14 @@
         <v>31.28402984</v>
       </c>
       <c r="E21">
-        <v>271.116</v>
+        <v>246.286</v>
       </c>
       <c r="F21">
         <v>24.83</v>
       </c>
       <c r="G21">
-        <f>100*(1.42+0.052*F21)</f>
-        <v>271.116</v>
+        <f t="shared" si="0"/>
+        <v>246.286</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1558,14 +1558,14 @@
         <v>31.2653378</v>
       </c>
       <c r="E22">
-        <v>180.50756</v>
+        <v>173.10226</v>
       </c>
       <c r="F22">
         <v>7.4053</v>
       </c>
       <c r="G22">
-        <f>100*(1.42+0.052*F22)</f>
-        <v>180.50756</v>
+        <f t="shared" si="0"/>
+        <v>173.10226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1582,14 +1582,14 @@
         <v>31.2653378</v>
       </c>
       <c r="E23">
-        <v>160.0908</v>
+        <v>156.6118</v>
       </c>
       <c r="F23">
         <v>3.479</v>
       </c>
       <c r="G23">
-        <f>100*(1.42+0.052*F23)</f>
-        <v>160.0908</v>
+        <f t="shared" si="0"/>
+        <v>156.6118</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1606,14 +1606,14 @@
         <v>31.2653378</v>
       </c>
       <c r="E24">
-        <v>180.48</v>
+        <v>173.08</v>
       </c>
       <c r="F24">
         <v>7.4</v>
       </c>
       <c r="G24">
-        <f>100*(1.42+0.052*F24)</f>
-        <v>180.48</v>
+        <f t="shared" si="0"/>
+        <v>173.08</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1630,14 +1630,14 @@
         <v>31.2653378</v>
       </c>
       <c r="E25">
-        <v>159.6046</v>
+        <v>156.2191</v>
       </c>
       <c r="F25">
         <v>3.3855</v>
       </c>
       <c r="G25">
-        <f>100*(1.42+0.052*F25)</f>
-        <v>159.6046</v>
+        <f t="shared" si="0"/>
+        <v>156.2191</v>
       </c>
     </row>
   </sheetData>

--- a/candidate_points.xlsx
+++ b/candidate_points.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21094" windowHeight="9805"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1035,13 +1035,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="16.2612612612613" customWidth="1"/>
+    <col min="3" max="3" width="16.2636363636364" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.5495495495495"/>
-    <col min="7" max="7" width="10.5495495495495"/>
+    <col min="5" max="5" width="10.5454545454545"/>
+    <col min="7" max="7" width="10.5454545454545"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1108,7 +1108,7 @@
         <v>3.6664</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G25" si="0">100*(1.42+0.042*F3)</f>
+        <f>100*(1.42+0.042*F3)</f>
         <v>157.39888</v>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>2.661</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G4:G31" si="0">100*(1.42+0.042*F4)</f>
         <v>153.1762</v>
       </c>
     </row>
@@ -1162,26 +1162,26 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
-        <v>121.1957982</v>
+        <v>121.2021117</v>
       </c>
       <c r="D6" s="3">
-        <v>31.27624149</v>
+        <v>31.29804887</v>
       </c>
       <c r="E6">
-        <v>164.2075</v>
+        <v>162.22384</v>
       </c>
       <c r="F6">
-        <v>5.2875</v>
+        <v>4.8152</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>164.2075</v>
+        <v>162.22384</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1189,23 +1189,23 @@
         <v>1</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3">
-        <v>121.2094775</v>
+        <v>121.1957982</v>
       </c>
       <c r="D7" s="3">
-        <v>31.27468382</v>
+        <v>31.27624149</v>
       </c>
       <c r="E7">
-        <v>178.9873</v>
+        <v>164.2075</v>
       </c>
       <c r="F7">
-        <v>8.8065</v>
+        <v>5.2875</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>178.9873</v>
+        <v>164.2075</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1213,23 +1213,23 @@
         <v>1</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="3">
-        <v>121.2052685</v>
+        <v>121.2094775</v>
       </c>
       <c r="D8" s="3">
         <v>31.27468382</v>
       </c>
       <c r="E8">
-        <v>158.78614</v>
+        <v>178.9873</v>
       </c>
       <c r="F8">
-        <v>3.9967</v>
+        <v>8.8065</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>158.78614</v>
+        <v>178.9873</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1237,71 +1237,71 @@
         <v>1</v>
       </c>
       <c r="B9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="3">
-        <v>121.1968505</v>
+        <v>121.2052685</v>
       </c>
       <c r="D9" s="3">
         <v>31.27468382</v>
       </c>
       <c r="E9">
-        <v>168.0274</v>
+        <v>158.78614</v>
       </c>
       <c r="F9">
-        <v>6.197</v>
+        <v>3.9967</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>168.0274</v>
+        <v>158.78614</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>121.2210522</v>
+        <v>121.1968505</v>
       </c>
       <c r="D10" s="3">
-        <v>31.27312615</v>
+        <v>31.27468382</v>
       </c>
       <c r="E10">
-        <v>167.86066</v>
+        <v>168.0274</v>
       </c>
       <c r="F10">
-        <v>6.1573</v>
+        <v>6.197</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>167.86066</v>
+        <v>168.0274</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>121.2252612</v>
+        <v>121.1884325</v>
       </c>
       <c r="D11" s="3">
-        <v>31.27624149</v>
+        <v>31.27468382</v>
       </c>
       <c r="E11">
-        <v>176.0641</v>
+        <v>159.98272</v>
       </c>
       <c r="F11">
-        <v>8.1105</v>
+        <v>4.2816</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>176.0641</v>
+        <v>159.98272</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1309,23 +1309,23 @@
         <v>2</v>
       </c>
       <c r="B12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3">
-        <v>121.2263135</v>
+        <v>121.2210522</v>
       </c>
       <c r="D12" s="3">
-        <v>31.27468382</v>
+        <v>31.27312615</v>
       </c>
       <c r="E12">
-        <v>162.7522</v>
+        <v>167.86066</v>
       </c>
       <c r="F12">
-        <v>4.941</v>
+        <v>6.1573</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>162.7522</v>
+        <v>167.86066</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1333,95 +1333,95 @@
         <v>2</v>
       </c>
       <c r="B13" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3">
-        <v>121.224209</v>
+        <v>121.2252612</v>
       </c>
       <c r="D13" s="3">
-        <v>31.27468382</v>
+        <v>31.27624149</v>
       </c>
       <c r="E13">
-        <v>161.28724</v>
+        <v>176.0641</v>
       </c>
       <c r="F13">
-        <v>4.5922</v>
+        <v>8.1105</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>161.28724</v>
+        <v>176.0641</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3">
         <v>3</v>
       </c>
-      <c r="B14" s="3">
-        <v>1</v>
-      </c>
       <c r="C14" s="3">
-        <v>121.241045</v>
+        <v>121.2263135</v>
       </c>
       <c r="D14" s="3">
-        <v>31.26845314</v>
+        <v>31.27468382</v>
       </c>
       <c r="E14">
-        <v>155.75626</v>
+        <v>162.7522</v>
       </c>
       <c r="F14">
-        <v>3.2753</v>
+        <v>4.941</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>155.75626</v>
+        <v>162.7522</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3">
-        <v>121.2431495</v>
+        <v>121.224209</v>
       </c>
       <c r="D15" s="3">
-        <v>31.26845314</v>
+        <v>31.27468382</v>
       </c>
       <c r="E15">
-        <v>148.2223</v>
+        <v>161.28724</v>
       </c>
       <c r="F15">
-        <v>1.4815</v>
+        <v>4.5922</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>148.2223</v>
+        <v>161.28724</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3">
-        <v>121.2442017</v>
+        <v>121.2221045</v>
       </c>
       <c r="D16" s="3">
-        <v>31.27001081</v>
+        <v>31.27468382</v>
       </c>
       <c r="E16">
-        <v>156.01708</v>
+        <v>163.65604</v>
       </c>
       <c r="F16">
-        <v>3.3374</v>
+        <v>5.1562</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>156.01708</v>
+        <v>163.65604</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1429,215 +1429,359 @@
         <v>3</v>
       </c>
       <c r="B17" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3">
-        <v>121.2263135</v>
+        <v>121.241045</v>
       </c>
       <c r="D17" s="3">
-        <v>31.27156848</v>
+        <v>31.26845314</v>
       </c>
       <c r="E17">
-        <v>167.39278</v>
+        <v>155.75626</v>
       </c>
       <c r="F17">
-        <v>6.0459</v>
+        <v>3.2753</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>167.39278</v>
+        <v>155.75626</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="3">
-        <v>121.2231567</v>
+        <v>121.2431495</v>
       </c>
       <c r="D18" s="3">
-        <v>31.28870285</v>
+        <v>31.26845314</v>
       </c>
       <c r="E18">
-        <v>149.5474</v>
+        <v>148.2223</v>
       </c>
       <c r="F18">
-        <v>1.797</v>
+        <v>1.4815</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>149.5474</v>
+        <v>148.2223</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3">
-        <v>121.2210522</v>
+        <v>121.2442017</v>
       </c>
       <c r="D19" s="3">
-        <v>31.28870285</v>
+        <v>31.27001081</v>
       </c>
       <c r="E19">
-        <v>268.02436</v>
+        <v>156.01708</v>
       </c>
       <c r="F19">
-        <v>30.0058</v>
+        <v>3.3374</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>268.02436</v>
+        <v>156.01708</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="3">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3">
         <v>4</v>
       </c>
-      <c r="B20" s="3">
-        <v>3</v>
-      </c>
       <c r="C20" s="3">
-        <v>121.2221045</v>
+        <v>121.2263135</v>
       </c>
       <c r="D20" s="3">
-        <v>31.28714518</v>
+        <v>31.27156848</v>
       </c>
       <c r="E20">
-        <v>392.88364</v>
+        <v>167.39278</v>
       </c>
       <c r="F20">
-        <v>59.7342</v>
+        <v>6.0459</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>392.88364</v>
+        <v>167.39278</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3">
         <v>121.232627</v>
       </c>
       <c r="D21" s="3">
-        <v>31.28402984</v>
+        <v>31.26845314</v>
       </c>
       <c r="E21">
-        <v>246.286</v>
+        <v>162.31708</v>
       </c>
       <c r="F21">
-        <v>24.83</v>
+        <v>4.8374</v>
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
-        <v>246.286</v>
+        <v>162.31708</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
       </c>
       <c r="C22" s="3">
-        <v>121.253672</v>
+        <v>121.2231567</v>
       </c>
       <c r="D22" s="3">
-        <v>31.2653378</v>
+        <v>31.28870285</v>
       </c>
       <c r="E22">
-        <v>173.10226</v>
+        <v>149.5474</v>
       </c>
       <c r="F22">
-        <v>7.4053</v>
+        <v>1.797</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>173.10226</v>
+        <v>149.5474</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
       </c>
       <c r="C23" s="3">
-        <v>121.2515675</v>
+        <v>121.2210522</v>
       </c>
       <c r="D23" s="3">
-        <v>31.2653378</v>
+        <v>31.28870285</v>
       </c>
       <c r="E23">
-        <v>156.6118</v>
+        <v>268.02436</v>
       </c>
       <c r="F23">
-        <v>3.479</v>
+        <v>30.0058</v>
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>156.6118</v>
+        <v>268.02436</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>121.249463</v>
+        <v>121.2221045</v>
       </c>
       <c r="D24" s="3">
-        <v>31.2653378</v>
+        <v>31.28714518</v>
       </c>
       <c r="E24">
-        <v>173.08</v>
+        <v>392.88364</v>
       </c>
       <c r="F24">
-        <v>7.4</v>
+        <v>59.7342</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
-        <v>173.08</v>
+        <v>392.88364</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
+        <v>121.232627</v>
+      </c>
+      <c r="D25" s="3">
+        <v>31.28402984</v>
+      </c>
+      <c r="E25">
+        <v>246.286</v>
+      </c>
+      <c r="F25">
+        <v>24.83</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>246.286</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>121.2294702</v>
+      </c>
+      <c r="D26" s="3">
+        <v>31.28247217</v>
+      </c>
+      <c r="E26">
+        <v>262.2712</v>
+      </c>
+      <c r="F26">
+        <v>28.636</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>262.2712</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3">
+        <v>5</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3">
+        <v>121.253672</v>
+      </c>
+      <c r="D27" s="3">
+        <v>31.2653378</v>
+      </c>
+      <c r="E27">
+        <v>173.10226</v>
+      </c>
+      <c r="F27">
+        <v>7.4053</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>173.10226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>121.2515675</v>
+      </c>
+      <c r="D28" s="3">
+        <v>31.2653378</v>
+      </c>
+      <c r="E28">
+        <v>156.6118</v>
+      </c>
+      <c r="F28">
+        <v>3.479</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>156.6118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3</v>
+      </c>
+      <c r="C29" s="3">
+        <v>121.249463</v>
+      </c>
+      <c r="D29" s="3">
+        <v>31.2653378</v>
+      </c>
+      <c r="E29">
+        <v>173.08</v>
+      </c>
+      <c r="F29">
+        <v>7.4</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>173.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3">
         <v>121.2473585</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D30" s="3">
         <v>31.2653378</v>
       </c>
-      <c r="E25">
+      <c r="E30">
         <v>156.2191</v>
       </c>
-      <c r="F25">
+      <c r="F30">
         <v>3.3855</v>
       </c>
-      <c r="G25">
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>156.2191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3">
+        <v>121.245254</v>
+      </c>
+      <c r="D31" s="3">
+        <v>31.2653378</v>
+      </c>
+      <c r="E31">
+        <v>199.52992</v>
+      </c>
+      <c r="F31">
+        <v>13.6976</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>199.52992</v>
       </c>
     </row>
   </sheetData>
